--- a/data/trans_orig/IP31C_2023-Clase-trans_orig.xlsx
+++ b/data/trans_orig/IP31C_2023-Clase-trans_orig.xlsx
@@ -541,7 +541,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -552,7 +552,7 @@
       <c r="I1" s="3" t="n"/>
       <c r="J1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="K1" s="3" t="n"/>
@@ -720,72 +720,72 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>100213</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>91201</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>106364</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>82,68%</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>75,24%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>87,75%</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>90007</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>82905</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>94879</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>88,49%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>81,51%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>93,28%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>138</t>
-        </is>
-      </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>113905</t>
+          <t>88095</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>105419</t>
+          <t>81742</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>121128</t>
+          <t>93283</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>84,26%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>77,99%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>92,96%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>203913</t>
+          <t>188308</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>193775</t>
+          <t>178136</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>212427</t>
+          <t>196212</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>86,08%</t>
+          <t>84,99%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>81,8%</t>
+          <t>80,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>88,56%</t>
         </is>
       </c>
     </row>
@@ -833,107 +833,107 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>2835</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,59%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>2,34%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="N5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
+        <is>
+          <t>717</t>
+        </is>
+      </c>
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>2327</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>2422</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,32%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>1,72%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>544</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>2213</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,23%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -946,72 +946,72 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>27</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>20279</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14086</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>28851</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>16,73%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>11,62%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>23,8%</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
           <t>15</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>11702</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>6830</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>18804</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>11,51%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>6,72%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>18,49%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>27</t>
-        </is>
-      </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>20726</t>
+          <t>12254</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>13731</t>
+          <t>7066</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>29529</t>
+          <t>18607</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>12,21%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>10,16%</t>
+          <t>7,04%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>32429</t>
+          <t>32533</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>23826</t>
+          <t>24804</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>42138</t>
+          <t>42190</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>13,69%</t>
+          <t>14,68%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>10,06%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>19,04%</t>
         </is>
       </c>
     </row>
@@ -1059,57 +1059,57 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>121209</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
           <t>152</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>101709</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>167</t>
-        </is>
-      </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>135176</t>
+          <t>100349</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1134,17 +1134,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>236886</t>
+          <t>221558</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1176,72 +1176,72 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>75278</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>68216</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>80720</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>84,59%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>76,66%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>90,71%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
           <t>124</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>83613</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>77747</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>87681</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>89,9%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>83,59%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>94,27%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>107</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>78962</t>
+          <t>85423</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>72420</t>
+          <t>79310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>84007</t>
+          <t>89609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>85,28%</t>
+          <t>89,86%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>78,21%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1251,32 +1251,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>162576</t>
+          <t>160702</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>154071</t>
+          <t>151391</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>169079</t>
+          <t>167619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>87,59%</t>
+          <t>87,31%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>83,01%</t>
+          <t>82,25%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>91,1%</t>
+          <t>91,07%</t>
         </is>
       </c>
     </row>
@@ -1289,72 +1289,72 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>782</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>2972</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,88%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>3,34%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>4</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>2824</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>708</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>6703</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2888</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>670</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>7006</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>3,04%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7,21%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K9" s="2" t="inlineStr">
-        <is>
-          <t>978</t>
-        </is>
-      </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3368</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>1,06%</t>
-        </is>
-      </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>7,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>3803</t>
+          <t>3670</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>1625</t>
+          <t>1349</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>8324</t>
+          <t>8279</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>4,5%</t>
         </is>
       </c>
     </row>
@@ -1402,72 +1402,72 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>12929</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>7700</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>19505</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>14,53%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>8,65%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>21,92%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>6569</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>3171</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>11686</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>3,41%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>12,56%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>12653</t>
+          <t>6756</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>7586</t>
+          <t>3332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18925</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>8,19%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>13,01%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>19223</t>
+          <t>19685</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>12906</t>
+          <t>13608</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>26378</t>
+          <t>28433</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>6,95%</t>
+          <t>7,39%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>14,21%</t>
+          <t>15,45%</t>
         </is>
       </c>
     </row>
@@ -1515,57 +1515,57 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>88990</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>88990</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>88990</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
           <t>137</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>93007</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>93007</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>93007</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>125</t>
-        </is>
-      </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>92594</t>
+          <t>95067</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1590,17 +1590,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185601</t>
+          <t>184057</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1632,72 +1632,72 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>51960</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>47298</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>54527</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>93,04%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>84,7%</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>97,64%</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>42380</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>36322</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>46088</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>85,76%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>73,5%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>93,26%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>58386</t>
+          <t>43325</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>54059</t>
+          <t>35034</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>60869</t>
+          <t>47412</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>93,67%</t>
+          <t>84,35%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>68,21%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>92,31%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1707,32 +1707,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>100766</t>
+          <t>95285</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>93604</t>
+          <t>85682</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>105402</t>
+          <t>100175</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>90,17%</t>
+          <t>88,88%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>79,92%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>94,32%</t>
+          <t>93,44%</t>
         </is>
       </c>
     </row>
@@ -1858,72 +1858,72 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3884</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>1317</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>8546</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>6,96%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>2,36%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>15,3%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>7040</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>3332</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>13098</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>14,24%</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>6,74%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>26,5%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>3948</t>
+          <t>8037</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>3950</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>8275</t>
+          <t>16328</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>15,65%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>7,69%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>31,79%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>10987</t>
+          <t>11921</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6351</t>
+          <t>7031</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>18149</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>9,83%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>20,08%</t>
         </is>
       </c>
     </row>
@@ -1971,57 +1971,57 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55844</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
           <t>70</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>49420</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>49420</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>49420</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J15" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>62334</t>
+          <t>51362</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2046,17 +2046,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>111753</t>
+          <t>107206</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2088,72 +2088,72 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>254</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>182248</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>174292</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>188130</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>92,36%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>88,33%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>95,35%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>249</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>173086</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>116166</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>200193</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>80,3%</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>53,9%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>92,88%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
-        <is>
-          <t>254</t>
-        </is>
-      </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>197969</t>
+          <t>157524</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>189319</t>
+          <t>146394</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>203966</t>
+          <t>164193</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>93,09%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>89,03%</t>
+          <t>82,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>95,91%</t>
+          <t>92,95%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2163,32 +2163,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>371056</t>
+          <t>339772</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>285427</t>
+          <t>326992</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>399249</t>
+          <t>349280</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>86,66%</t>
+          <t>90,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>87,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>93,24%</t>
+          <t>93,4%</t>
         </is>
       </c>
     </row>
@@ -2201,72 +2201,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>1952</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>5946</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>0,99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3,01%</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>29664</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>1803</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>92148</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>13,76%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="inlineStr">
-        <is>
-          <t>42,75%</t>
-        </is>
-      </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>2129</t>
+          <t>5610</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1592</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7670</t>
+          <t>17609</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>9,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2276,32 +2276,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31793</t>
+          <t>7562</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3534</t>
+          <t>2793</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>130869</t>
+          <t>17987</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>30,56%</t>
+          <t>4,81%</t>
         </is>
       </c>
     </row>
@@ -2319,32 +2319,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>12787</t>
+          <t>13114</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>6870</t>
+          <t>7837</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>20658</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3,19%</t>
+          <t>3,97%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>9,58%</t>
+          <t>10,73%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2354,32 +2354,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>12560</t>
+          <t>13506</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>7317</t>
+          <t>8245</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>19930</t>
+          <t>20968</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,44%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>11,87%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2389,32 +2389,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>25347</t>
+          <t>26620</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>17258</t>
+          <t>18321</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>36224</t>
+          <t>38228</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>5,92%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,46%</t>
+          <t>10,22%</t>
         </is>
       </c>
     </row>
@@ -2427,57 +2427,57 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>273</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>197313</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
           <t>271</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>215537</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>273</t>
-        </is>
-      </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>212658</t>
+          <t>176640</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2502,17 +2502,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>428196</t>
+          <t>373953</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2544,72 +2544,72 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>133201</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>123903</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>138443</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>92,04%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>85,61%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>95,66%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
           <t>163</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>109289</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>103620</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>112503</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr">
-        <is>
-          <t>94,62%</t>
-        </is>
-      </c>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>89,71%</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="inlineStr">
-        <is>
-          <t>97,4%</t>
-        </is>
-      </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>178</t>
-        </is>
-      </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>147101</t>
+          <t>108856</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>138692</t>
+          <t>102968</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>152180</t>
+          <t>112329</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>92,72%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>87,42%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>95,92%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,32 +2619,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>256390</t>
+          <t>242057</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>246264</t>
+          <t>232777</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>262920</t>
+          <t>248916</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>93,03%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>89,82%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>95,9%</t>
+          <t>95,67%</t>
         </is>
       </c>
     </row>
@@ -2657,92 +2657,92 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>3519</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>10683</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>2,43%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>7,38%</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="K21" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="L21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="M21" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G21" s="2" t="inlineStr">
+      <c r="N21" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H21" s="2" t="inlineStr">
+      <c r="O21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I21" s="2" t="inlineStr">
+      <c r="P21" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J21" s="2" t="inlineStr">
+      <c r="Q21" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="K21" s="2" t="inlineStr">
-        <is>
-          <t>3690</t>
-        </is>
-      </c>
-      <c r="L21" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="M21" s="2" t="inlineStr">
-        <is>
-          <t>10678</t>
-        </is>
-      </c>
-      <c r="N21" s="2" t="inlineStr">
-        <is>
-          <t>2,33%</t>
-        </is>
-      </c>
-      <c r="O21" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="P21" s="2" t="inlineStr">
-        <is>
-          <t>6,73%</t>
-        </is>
-      </c>
-      <c r="Q21" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>3690</t>
+          <t>3519</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>946</t>
+          <t>893</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10740</t>
+          <t>9898</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2757,7 +2757,7 @@
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,8%</t>
         </is>
       </c>
     </row>
@@ -2770,72 +2770,72 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>8003</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>3916</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>15883</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>5,53%</t>
+        </is>
+      </c>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>2,71%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>10,97%</t>
+        </is>
+      </c>
+      <c r="J22" s="2" t="inlineStr">
+        <is>
           <t>8</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>6220</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>3006</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>11889</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr">
-        <is>
-          <t>5,38%</t>
-        </is>
-      </c>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>2,6%</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="inlineStr">
-        <is>
-          <t>10,29%</t>
-        </is>
-      </c>
-      <c r="J22" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>7862</t>
+          <t>6610</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>3707</t>
+          <t>3137</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>14676</t>
+          <t>12498</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2845,32 +2845,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>14082</t>
+          <t>14614</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8439</t>
+          <t>8802</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22398</t>
+          <t>23187</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>8,17%</t>
+          <t>8,91%</t>
         </is>
       </c>
     </row>
@@ -2883,57 +2883,57 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>144724</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>144724</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>144724</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>171</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>115509</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
-        <is>
-          <t>191</t>
-        </is>
-      </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>158652</t>
+          <t>115466</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2958,17 +2958,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>260190</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>260190</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>274161</t>
+          <t>260190</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -3000,72 +3000,72 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>58534</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>52635</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>62229</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>88,87%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>79,92%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>94,48%</t>
+        </is>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
           <t>95</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>66316</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>62583</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>67976</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr">
-        <is>
-          <t>97,03%</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>91,57%</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="inlineStr">
-        <is>
-          <t>99,46%</t>
-        </is>
-      </c>
-      <c r="J24" s="2" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>61884</t>
+          <t>67836</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>55890</t>
+          <t>64007</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>65613</t>
+          <t>69563</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>89,65%</t>
+          <t>97,06%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>80,96%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,32 +3075,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>128200</t>
+          <t>126370</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>121673</t>
+          <t>118971</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>132403</t>
+          <t>130663</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>93,09%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>87,64%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>96,38%</t>
+          <t>96,25%</t>
         </is>
       </c>
     </row>
@@ -3113,107 +3113,107 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>3300</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>0,89%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>5,01%</t>
+        </is>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="K25" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr">
+      <c r="M25" s="2" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G25" s="2" t="inlineStr">
+      <c r="N25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H25" s="2" t="inlineStr">
+      <c r="O25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="I25" s="2" t="inlineStr">
+      <c r="P25" s="2" t="inlineStr">
         <is>
           <t>—%</t>
         </is>
       </c>
-      <c r="J25" s="2" t="inlineStr">
+      <c r="Q25" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K25" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="L25" s="2" t="inlineStr">
+      <c r="R25" s="2" t="inlineStr">
+        <is>
+          <t>586</t>
+        </is>
+      </c>
+      <c r="S25" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M25" s="2" t="inlineStr">
-        <is>
-          <t>2551</t>
-        </is>
-      </c>
-      <c r="N25" s="2" t="inlineStr">
-        <is>
-          <t>0,84%</t>
-        </is>
-      </c>
-      <c r="O25" s="2" t="inlineStr">
+      <c r="T25" s="2" t="inlineStr">
+        <is>
+          <t>3024</t>
+        </is>
+      </c>
+      <c r="U25" s="2" t="inlineStr">
+        <is>
+          <t>0,43%</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P25" s="2" t="inlineStr">
-        <is>
-          <t>3,69%</t>
-        </is>
-      </c>
-      <c r="Q25" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R25" s="2" t="inlineStr">
-        <is>
-          <t>578</t>
-        </is>
-      </c>
-      <c r="S25" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T25" s="2" t="inlineStr">
-        <is>
-          <t>2937</t>
-        </is>
-      </c>
-      <c r="U25" s="2" t="inlineStr">
-        <is>
-          <t>0,42%</t>
-        </is>
-      </c>
-      <c r="V25" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,23%</t>
         </is>
       </c>
     </row>
@@ -3226,72 +3226,72 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>6743</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>3001</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>12456</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>10,24%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>4,56%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>18,91%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
           <t>3</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>2032</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>372</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>5765</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr">
-        <is>
-          <t>2,97%</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>0,54%</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="inlineStr">
-        <is>
-          <t>8,43%</t>
-        </is>
-      </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>6569</t>
+          <t>2053</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>3082</t>
+          <t>326</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>13088</t>
+          <t>5882</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>8,42%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,32 +3301,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>8600</t>
+          <t>8796</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>4632</t>
+          <t>4518</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>14727</t>
+          <t>16011</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,79%</t>
         </is>
       </c>
     </row>
@@ -3339,57 +3339,57 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>84</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>65863</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
           <t>98</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>68348</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>68348</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>68348</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J27" s="2" t="inlineStr">
-        <is>
-          <t>84</t>
-        </is>
-      </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>69031</t>
+          <t>69889</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3414,17 +3414,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>137378</t>
+          <t>135752</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3456,72 +3456,72 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>827</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>601434</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>585866</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>616404</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>89,24%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>86,93%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>91,46%</t>
+        </is>
+      </c>
+      <c r="J28" s="2" t="inlineStr">
+        <is>
           <t>829</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>564691</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>489749</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>593774</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr">
-        <is>
-          <t>87,75%</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>76,1%</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="inlineStr">
-        <is>
-          <t>92,27%</t>
-        </is>
-      </c>
-      <c r="J28" s="2" t="inlineStr">
-        <is>
-          <t>827</t>
-        </is>
-      </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>658208</t>
+          <t>551059</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>642621</t>
+          <t>536872</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>673791</t>
+          <t>563524</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>90,11%</t>
+          <t>90,52%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>87,98%</t>
+          <t>88,19%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>92,24%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3531,32 +3531,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>1222899</t>
+          <t>1152493</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>1136371</t>
+          <t>1133023</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>1253057</t>
+          <t>1172386</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>89,0%</t>
+          <t>89,85%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>91,2%</t>
+          <t>91,4%</t>
         </is>
       </c>
     </row>
@@ -3569,72 +3569,72 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>7556</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>3691</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>14841</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>1,12%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>0,55%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,2%</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
           <t>9</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
-        <is>
-          <t>32489</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="inlineStr">
-        <is>
-          <t>4522</t>
-        </is>
-      </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>113576</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>5,05%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="inlineStr">
-        <is>
-          <t>17,65%</t>
-        </is>
-      </c>
-      <c r="J29" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>7919</t>
+          <t>8497</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>3721</t>
+          <t>3588</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>16072</t>
+          <t>20139</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3644,32 +3644,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>40408</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>11809</t>
+          <t>9147</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>140069</t>
+          <t>26982</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>2,1%</t>
         </is>
       </c>
     </row>
@@ -3682,72 +3682,72 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>83</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>64953</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>49837</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>78829</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>9,64%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>7,39%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>11,7%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
           <t>61</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>46350</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
-        <is>
-          <t>34837</t>
-        </is>
-      </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>58335</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>7,2%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>5,41%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>9,06%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
-        <is>
-          <t>83</t>
-        </is>
-      </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>64318</t>
+          <t>49217</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>51017</t>
+          <t>38372</t>
         </is>
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>80275</t>
+          <t>63748</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
         <is>
-          <t>6,98%</t>
+          <t>6,3%</t>
         </is>
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>10,99%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -3757,32 +3757,32 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>110668</t>
+          <t>114170</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
         <is>
-          <t>93147</t>
+          <t>94932</t>
         </is>
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>130659</t>
+          <t>132340</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>8,05%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>9,51%</t>
+          <t>10,32%</t>
         </is>
       </c>
     </row>
@@ -3795,57 +3795,57 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>920</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>673943</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>673943</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>673943</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
           <t>899</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>643530</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>643530</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>643530</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="J31" s="2" t="inlineStr">
-        <is>
-          <t>920</t>
-        </is>
-      </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>730445</t>
+          <t>608773</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>730445</t>
+          <t>608773</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>730445</t>
+          <t>608773</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -3870,17 +3870,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>1373975</t>
+          <t>1282716</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>1373975</t>
+          <t>1282716</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>1373975</t>
+          <t>1282716</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
